--- a/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/bottom-full-1.xlsx
+++ b/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/bottom-full-1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\przemyslaw.klys.EVOTEC\.codex\worktrees\excel-csv-quality\OfficeIMO\OfficeIMO.TestAssets\Documents\ExcelPivotCorpus\AllErrorRanking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E536EAF2-3348-4A0E-8E44-D54123A89CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{42E65299-88D0-4CA2-99F1-175E04084589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{3ADA8AE5-5F05-4659-9EF9-4CE63428C820}"/>
+    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{6778138B-1D1A-4B0C-A0B5-B78370777B25}"/>
   </bookViews>
   <sheets>
     <sheet name="Grouped" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="95" r:id="rId3"/>
+    <pivotCache cacheId="127" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.576878472224" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="7" xr:uid="{1B964588-EA8D-43FC-A29E-0F0F62C442F5}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.57945138889" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="7" xr:uid="{70F55C45-C283-4951-BFE3-2C2384A8AE61}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:B8" sheet="Source"/>
   </cacheSource>
@@ -196,7 +196,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FEBB48BD-E1D8-4E12-893F-0BF1BF168DC9}" name="AllErrorPivot" cacheId="95" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FE4785ED-861D-4633-8A70-21A3AFC2676E}" name="AllErrorPivot" cacheId="127" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" measureFilter="1">
@@ -567,7 +567,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AA1BD6D-45FA-40E4-B278-9AC582502543}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CC54621-7D34-4474-B6ED-5CF4C05090DD}">
   <dimension ref="A4:B6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -605,7 +605,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F41C6F3-299F-476A-8B67-D8F7CD306DC7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B878BDB2-BA16-46CB-B597-898D8FB027A3}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
